--- a/artfynd/A 50584-2025 artfynd.xlsx
+++ b/artfynd/A 50584-2025 artfynd.xlsx
@@ -1112,7 +1112,7 @@
         <v>127225111</v>
       </c>
       <c r="B6" t="n">
-        <v>91368</v>
+        <v>91337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>127225118</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
         <v>127225068</v>
       </c>
       <c r="B8" t="n">
-        <v>80161</v>
+        <v>80143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>127225125</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>127225091</v>
       </c>
       <c r="B10" t="n">
-        <v>80168</v>
+        <v>80150</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>127225084</v>
       </c>
       <c r="B11" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>127225123</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
         <v>127225120</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         <v>127225097</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>127225113</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,7 +2082,7 @@
         <v>127225122</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>127225074</v>
       </c>
       <c r="B17" t="n">
-        <v>78391</v>
+        <v>78373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>127225127</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>127225116</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>127225105</v>
       </c>
       <c r="B20" t="n">
-        <v>56855</v>
+        <v>56840</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 50584-2025 artfynd.xlsx
+++ b/artfynd/A 50584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118675941</v>
+        <v>117766265</v>
       </c>
       <c r="B2" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,13 +714,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801049</v>
+        <v>800646</v>
       </c>
       <c r="R2" t="n">
-        <v>7403867</v>
+        <v>7404073</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121152420</v>
+        <v>127415026</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801126</v>
+        <v>800601</v>
       </c>
       <c r="R3" t="n">
-        <v>7403880</v>
+        <v>7404205</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,12 +850,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -897,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126017325</v>
+        <v>127415031</v>
       </c>
       <c r="B4" t="n">
-        <v>91245</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,13 +926,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801050</v>
+        <v>801052</v>
       </c>
       <c r="R4" t="n">
-        <v>7403864</v>
+        <v>7403867</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1003,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126017323</v>
+        <v>126017325</v>
       </c>
       <c r="B5" t="n">
-        <v>80083</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>800666</v>
+        <v>801050</v>
       </c>
       <c r="R5" t="n">
-        <v>7404142</v>
+        <v>7403864</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127225111</v>
+        <v>127415030</v>
       </c>
       <c r="B6" t="n">
-        <v>91368</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1120,37 +1110,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Simonslandet, Lu lm</t>
+          <t>Neitaskaite, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>801045</v>
+        <v>800648</v>
       </c>
       <c r="R6" t="n">
-        <v>7403861</v>
+        <v>7404072</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1174,12 +1168,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,26 +1193,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127225118</v>
+        <v>127225113</v>
       </c>
       <c r="B7" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1241,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>800749</v>
+        <v>800817</v>
       </c>
       <c r="R7" t="n">
-        <v>7404085</v>
+        <v>7404104</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1303,32 +1302,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127225068</v>
+        <v>127225116</v>
       </c>
       <c r="B8" t="n">
-        <v>80161</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1338,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>800813</v>
+        <v>800828</v>
       </c>
       <c r="R8" t="n">
-        <v>7404222</v>
+        <v>7404118</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1400,14 +1399,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127225125</v>
+        <v>127225118</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1435,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>801153</v>
+        <v>800749</v>
       </c>
       <c r="R9" t="n">
-        <v>7403864</v>
+        <v>7404085</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1497,32 +1496,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127225091</v>
+        <v>127225120</v>
       </c>
       <c r="B10" t="n">
-        <v>80168</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>800756</v>
+        <v>800870</v>
       </c>
       <c r="R10" t="n">
-        <v>7404083</v>
+        <v>7404019</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1594,32 +1593,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127225084</v>
+        <v>127225122</v>
       </c>
       <c r="B11" t="n">
-        <v>97351</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1629,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>800818</v>
+        <v>800973</v>
       </c>
       <c r="R11" t="n">
-        <v>7403953</v>
+        <v>7403839</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1694,11 +1693,11 @@
         <v>127225123</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1788,14 +1787,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127225120</v>
+        <v>127225125</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1823,10 +1822,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>800870</v>
+        <v>801153</v>
       </c>
       <c r="R13" t="n">
-        <v>7404019</v>
+        <v>7403864</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1885,10 +1884,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127225097</v>
+        <v>127225127</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1896,21 +1895,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1920,10 +1919,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>800844</v>
+        <v>801235</v>
       </c>
       <c r="R14" t="n">
-        <v>7404187</v>
+        <v>7403841</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1982,14 +1981,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127225113</v>
+        <v>127415028</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2010,20 +2009,24 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Simonslandet, Lu lm</t>
+          <t>Neitaskaite, Lu lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>800817</v>
+        <v>800688</v>
       </c>
       <c r="R15" t="n">
-        <v>7404104</v>
+        <v>7404145</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2047,12 +2050,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2067,44 +2075,44 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127225122</v>
+        <v>127225074</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>78685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6443</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2114,10 +2122,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>800973</v>
+        <v>800820</v>
       </c>
       <c r="R16" t="n">
-        <v>7403839</v>
+        <v>7404131</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2176,48 +2184,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127225074</v>
+        <v>121152420</v>
       </c>
       <c r="B17" t="n">
-        <v>78391</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6443</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Simonslandet, Lu lm</t>
+          <t>Neitaskaite, Lu lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>800820</v>
+        <v>801126</v>
       </c>
       <c r="R17" t="n">
-        <v>7404131</v>
+        <v>7403880</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2241,12 +2253,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2261,22 +2278,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127225127</v>
+        <v>126017323</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2284,37 +2301,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Simonslandet, Lu lm</t>
+          <t>Neitaskaite, Lu lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>801235</v>
+        <v>800666</v>
       </c>
       <c r="R18" t="n">
-        <v>7403841</v>
+        <v>7404142</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2338,12 +2359,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2358,22 +2384,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127225116</v>
+        <v>127415027</v>
       </c>
       <c r="B19" t="n">
-        <v>79029</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2381,37 +2407,41 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Simonslandet, Lu lm</t>
+          <t>Neitaskaite, Lu lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>800828</v>
+        <v>800766</v>
       </c>
       <c r="R19" t="n">
-        <v>7404118</v>
+        <v>7404338</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2435,12 +2465,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2455,44 +2490,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127225105</v>
+        <v>127225068</v>
       </c>
       <c r="B20" t="n">
-        <v>56855</v>
+        <v>80461</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2502,10 +2537,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>800815</v>
+        <v>800813</v>
       </c>
       <c r="R20" t="n">
-        <v>7404140</v>
+        <v>7404222</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2564,52 +2599,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127415031</v>
+        <v>127225091</v>
       </c>
       <c r="B21" t="n">
-        <v>91348</v>
+        <v>80468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1108</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Neitaskaite, Lu lm</t>
+          <t>Simonslandet, Lu lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>801052</v>
+        <v>800756</v>
       </c>
       <c r="R21" t="n">
-        <v>7403867</v>
+        <v>7404083</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2633,17 +2664,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2658,64 +2684,60 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127415026</v>
+        <v>127225105</v>
       </c>
       <c r="B22" t="n">
-        <v>91648</v>
+        <v>57132</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Neitaskaite, Lu lm</t>
+          <t>Simonslandet, Lu lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>800601</v>
+        <v>800815</v>
       </c>
       <c r="R22" t="n">
-        <v>7404205</v>
+        <v>7404140</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2739,17 +2761,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2764,44 +2781,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127415028</v>
+        <v>126017324</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>99035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2815,13 +2832,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>800688</v>
+        <v>801010</v>
       </c>
       <c r="R23" t="n">
-        <v>7404145</v>
+        <v>7403864</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2845,12 +2862,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -2882,10 +2899,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127735578</v>
+        <v>127225097</v>
       </c>
       <c r="B24" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2910,24 +2927,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Neitaskaite, Lu lm</t>
+          <t>Simonslandet, Lu lm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>800851</v>
+        <v>800844</v>
       </c>
       <c r="R24" t="n">
-        <v>7404179</v>
+        <v>7404187</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2951,17 +2964,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,15 +2984,315 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127735578</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Neitaskaite, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>800851</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7404179</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127225084</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Simonslandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>800818</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7403953</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127225087</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Simonslandet, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>800974</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7403787</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50584-2025 artfynd.xlsx
+++ b/artfynd/A 50584-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117766265</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415031</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017325</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415030</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225113</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225116</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225118</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225120</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225122</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1784,6 +1839,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225123</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1881,6 +1941,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225125</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1978,6 +2043,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225127</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2084,6 +2154,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415028</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2181,6 +2256,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225074</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2287,6 +2367,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121152420</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2393,6 +2478,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017323</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2499,6 +2589,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415027</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2596,6 +2691,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225068</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2693,6 +2793,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225091</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2790,6 +2895,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225105</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2896,6 +3006,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126017324</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2993,6 +3108,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225097</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3099,6 +3219,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127735578</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3196,6 +3321,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225084</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3293,8 +3423,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127225087</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>